--- a/stock_screener/output/report_20260731.xlsx
+++ b/stock_screener/output/report_20260731.xlsx
@@ -528,7 +528,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 箱波均戰法 — 選股結果　　2026-07-31 02:16</t>
+          <t>📊 箱波均戰法 — 選股結果　　2026-07-31 09:41</t>
         </is>
       </c>
     </row>
@@ -602,12 +602,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>107.5</v>
+        <v>35.95000076293945</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.05911330049261083</v>
+        <v>0.08446452815016305</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1823</v>
+        <v>94709</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -634,10 +634,14 @@
           <t>⏸️ 中性</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>過而不破</t>
+        </is>
+      </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>📈 短多</t>
+          <t>📈 多頭排列</t>
         </is>
       </c>
     </row>
@@ -647,12 +651,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -661,17 +665,17 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>35.04999923706055</v>
+        <v>109.5</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.05731516210333767</v>
+        <v>0.07881773399014778</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>32957</v>
+        <v>4202</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>止跌缺口</t>
+          <t>過而不破</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -679,14 +683,10 @@
           <t>⏸️ 中性</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>過而不破</t>
-        </is>
-      </c>
+      <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>📈 多頭排列</t>
+          <t>📈 短多</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>台灣虎航</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -710,28 +710,32 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>57.20000076293945</v>
+        <v>130</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.04189433830846739</v>
+        <v>0.04838709677419355</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1484</v>
+        <v>32791</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>過而不破</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>⏸️ 中性</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>📈 多頭排列</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>多方炮</t>
+        </is>
+      </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>📈 短多</t>
+          <t>📈 多頭排列</t>
         </is>
       </c>
     </row>
@@ -741,12 +745,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台灣虎航</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -755,28 +759,28 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>128</v>
+        <v>57.40000152587891</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.04553733935365271</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>8316</v>
+        <v>3300</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>止跌缺口</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>📈 多頭排列</t>
+          <t>過而不破</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>⏸️ 中性</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>📈 多頭排列</t>
+          <t>📈 短多</t>
         </is>
       </c>
     </row>
@@ -800,13 +804,13 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>16.79999923706055</v>
+        <v>16.75</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.009008986304320059</v>
+        <v>0.006006029054705395</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1307</v>
+        <v>2573</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
